--- a/resources/templates/usdm-report-template.xlsx
+++ b/resources/templates/usdm-report-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GerryCampion\Code\cdisc-rules-engine\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE3BDED-81DC-46AF-8ECD-7B2F89F8455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79E2183-EF7B-4621-8BA8-68E7710FF2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="6" r:id="rId1"/>
@@ -323,47 +323,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEDAA00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEDAA00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <color auto="1"/>
@@ -371,26 +331,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC94543"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -430,7 +370,27 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFC94543"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFEDAA00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -499,8 +459,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="CDISC" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="CDISC" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="secondRowStripe" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1068,7 +1028,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"not configured"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11186,16 +11146,16 @@
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="C1:D1048576">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"Notice"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"Warning"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"Error"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"Reject"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13015,17 +12975,17 @@
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
-      <formula>"ISSUE_REPORTED"</formula>
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"SUCCESS"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"SKIPPED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>"SUCCESS"</formula>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"ISSUE REPORTED"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
-      <formula>"EXECUTION_ERROR"</formula>
+      <formula>"EXECUTION ERROR"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13034,12 +12994,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="de0c653c-2bd3-43b1-95fa-012c57f61cfe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="848a8810-16a6-4d79-96d3-e3dfb86099b7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13315,22 +13279,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="de0c653c-2bd3-43b1-95fa-012c57f61cfe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="848a8810-16a6-4d79-96d3-e3dfb86099b7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9F60A92-6BFE-4C8E-AEB2-AFC039296A60}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C23D74-9542-4171-A552-025893E8AF6E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="de0c653c-2bd3-43b1-95fa-012c57f61cfe"/>
+    <ds:schemaRef ds:uri="848a8810-16a6-4d79-96d3-e3dfb86099b7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13356,13 +13320,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20C23D74-9542-4171-A552-025893E8AF6E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9F60A92-6BFE-4C8E-AEB2-AFC039296A60}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="de0c653c-2bd3-43b1-95fa-012c57f61cfe"/>
-    <ds:schemaRef ds:uri="848a8810-16a6-4d79-96d3-e3dfb86099b7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>